--- a/sources/baek_step8.xlsx
+++ b/sources/baek_step8.xlsx
@@ -421,11 +421,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col hidden="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col hidden="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
@@ -3730,22 +3730,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>– 3 [~f_~b]</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1,2,3 [~f_~b]</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>– High Kick [FLA]</t>
+          <t>– High Kick</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Double Punch – High Kick [FLA]</t>
+          <t>Double Punch – High Kick</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4143,22 +4148,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1,2,3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>1,2,3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Double Punch – Black Widow [FLA]</t>
+          <t>Double Punch – Black Widow</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5402,22 +5412,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Black Widow [FLA]</t>
+          <t>Black Widow</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Black Widow [FLA]</t>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5815,22 +5830,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WS+3,4&lt;4,3 [~f_~b]</t>
+          <t>WS+3,4&lt;4,3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WS+3,4&lt;4,3 [~f_~b]</t>
+          <t>WS+3,4&lt;4,3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Eliminator [FLA]</t>
+          <t>Eliminator</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eliminator [FLA]</t>
+          <t>Eliminator</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6616,22 +6636,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>uf,N,3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>uf,N,3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Baek Hop – Black Widow [FLA]</t>
+          <t>Baek Hop – Black Widow</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7228,27 +7253,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3+4 [f_b]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3+4 [f_b]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>uf+3+4 [f_b]</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7753,22 +7783,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>f+4&lt;3 [f_b]</t>
+          <t>f+4&lt;3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f+4&lt;3 [f_b]</t>
+          <t>f+4&lt;3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Heel Knife [FLA]</t>
+          <t>Heel Knife</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heel Knife [FLA]</t>
+          <t>Heel Knife</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7962,22 +7997,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WS+4&lt;4&lt;3 [f_b]</t>
+          <t>WS+4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WS+4&lt;4&lt;3 [f_b]</t>
+          <t>WS+4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8171,22 +8211,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>df+4~4&lt;3 [f_b]</t>
+          <t>df+4~4&lt;3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>df+4~4&lt;3 [f_b]</t>
+          <t>df+4~4&lt;3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8380,27 +8425,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FC+4,3,3&lt;3 [f_b]</t>
+          <t>FC+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FC+4,3,3&lt;3 [f_b]</t>
+          <t>FC+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>d+4,3,3&lt;3 [f_b]</t>
+          <t>d+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Baek Rush [FLA]</t>
+          <t>Baek Rush</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Baek Rush [FLA]</t>
+          <t>Baek Rush</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8656,22 +8706,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>b+1+2 [~B]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>b+1+2 [~B]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>High &amp; Mid Punch Parry [FLA]</t>
+          <t>High &amp; Mid Punch Parry</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>High &amp; Mid Punch Parry [FLA]</t>
+          <t>High &amp; Mid Punch Parry</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>(~B)FLA</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9422,22 +9477,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3,4,4,3 [f_b]</t>
+          <t>3,4,4,3</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3,4,4,3 [f_b]</t>
+          <t>3,4,4,3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Flamingo Eliminator [FLA]</t>
+          <t>Flamingo Eliminator</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Flamingo Eliminator [FLA]</t>
+          <t>Flamingo Eliminator</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9765,22 +9825,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N+4 [f_b]</t>
+          <t>N+4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>N+4 [f_b]</t>
+          <t>N+4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -10001,12 +10066,12 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -10243,12 +10308,12 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -10320,7 +10385,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -10564,12 +10629,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>hhhlmmmlm[!]</t>
+          <t>hhhlmmmlm!</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>hhhlmmmlm[!]</t>
+          <t>hhhlmmmlm!</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">

--- a/sources/baek_step8.xlsx
+++ b/sources/baek_step8.xlsx
@@ -1000,6 +1000,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
@@ -1062,6 +1067,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
@@ -1122,6 +1132,11 @@
       <c r="U10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>c1e72722-088e-4713-997a-36ef818af837</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -10590,6 +10605,11 @@
           <t>hhlmmmhmlm</t>
         </is>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
+        </is>
+      </c>
       <c r="Z118" t="inlineStr">
         <is>
           <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
@@ -10635,6 +10655,11 @@
       <c r="S119" t="inlineStr">
         <is>
           <t>hhhlmmmlm!</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>26c9b6a0-30d4-4ef8-b80e-04220b821fe5</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
